--- a/data/transfers.xlsx
+++ b/data/transfers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1678,6 +1678,2076 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:23:04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TRX-100028</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:31:03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>TRX-100029</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:43:55</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>TRX-100030</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:44:29</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TRX-100031</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-14 14:29:12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>TRX-100032</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-14 14:29:48</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>TRX-100033</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-14 14:31:45</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>45678945</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>20</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Web Banking</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>TRX-100034</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:04:10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>100</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>TRX-100035</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:04:43</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>TRX-100036</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:14:25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>TRX-100037</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:14:58</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>TRX-100038</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:17:38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>TRX-100039</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:18:13</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>TRX-100040</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:45:54</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>100</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>TRX-100041</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:46:28</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>TRX-100042</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:51:12</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>100</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>TRX-100043</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:51:47</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>TRX-100044</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:55:13</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>100</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>TRX-100045</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:55:48</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>TRX-100046</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:13:17</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>TRX-100047</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:13:50</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>TRX-100048</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:17:47</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TRX-100049</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:18:20</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TRX-100050</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:21:32</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>100</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>TRX-100051</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:22:10</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>TRX-100052</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:25:46</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>100</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>TRX-100053</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:26:18</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TRX-100054</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:33:34</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>100</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>TRX-100055</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:34:10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>TRX-100056</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:36:14</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>TRX-100057</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:36:57</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>TRX-100058</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-16 11:39:24</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>100</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TRX-100059</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-16 11:39:57</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>TRX-100060</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:25:05</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>100</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>TRX-100061</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:25:36</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>TRX-100062</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:37:47</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>100</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>TRX-100063</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:38:19</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>TRX-100064</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:49:13</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>100</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>TRX-100065</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:49:45</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>TRX-100066</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:06:24</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>22223333</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>100</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>TRX-100067</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:06:55</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>TRX-100068</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:14:40</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>22223333</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>100</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TRX-100069</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:15:12</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>TRX-100070</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:09:17</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>22223333</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>100</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TRX-100071</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:09:59</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>TRX-100072</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:34:01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>100</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>TRX-100073</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transfers.xlsx
+++ b/data/transfers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3748,6 +3748,186 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:44:26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>100</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>TRX-100074</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:44:58</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>77779999</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>TRX-100075</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:59:34</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>77779999</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>TRX-100076</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:59:44</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>77779999</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>TRX-100077</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transfers.xlsx
+++ b/data/transfers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3928,6 +3928,366 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:04:52</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>100</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>TRX-100078</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:06:28</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>77779999</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>TRX-100079</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:44:37</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>100</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>TRX-100080</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:46:08</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>77779999</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>TRX-100081</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:54:50</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>100</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>TRX-100082</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:55:25</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>77779999</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>TRX-100083</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:13:16</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>100</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>TRX-100084</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:13:47</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>77779999</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>12312312</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Web Banking</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>TRX-100085</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
